--- a/spreadsheets/franchises.xlsx
+++ b/spreadsheets/franchises.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4829262-E7C6-6B41-8C97-34E129E6C4A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71870541-4273-8347-BFBB-18746C44DBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17400" xr2:uid="{560E9FB9-65B9-9A4C-9447-806357BA28D7}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{560E9FB9-65B9-9A4C-9447-806357BA28D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -999,7 +999,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1041,13 +1041,42 @@
       <name val="Aptos Display"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2937"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F2937"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1059,36 +1088,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FFE5E7EB"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1100,19 +1113,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1446,38 +1466,60 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{FCCB346D-A6B4-8C47-96DF-71DE62038C26}">
+  <we:reference id="29673e3c-d826-4f00-92ee-162334a52b1a" version="1.0.0.8" store="EXCatalog" storeType="EXCatalog"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="Office.AutoShowTaskpaneWithDocument" value="true"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC382C8-FAC7-9345-92A5-4AC6D3C427D2}">
   <dimension ref="A1:AM59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="32" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="35.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="41" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="46.83203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="46" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="37" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="27.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="34.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="43.83203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="44.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="28.5" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="34.83203125" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="16" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="35.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="35.83203125" style="5" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="32" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="16.83203125" bestFit="1" customWidth="1"/>
@@ -1491,2115 +1533,2609 @@
     <col min="39" max="39" width="36" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:39" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="P1" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="Q1" s="11" t="s">
+      <c r="Q1" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="T1" s="11" t="s">
+      <c r="T1" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="U1" s="11" t="s">
+      <c r="U1" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="X1" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-    </row>
-    <row r="2" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10" t="s">
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+    </row>
+    <row r="2" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="N2" s="12" t="s">
+      <c r="N2" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="R2" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="S2" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="T2" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="U2" s="14" t="s">
+      <c r="U2" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="X2" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="7"/>
-      <c r="AD2" s="7"/>
-      <c r="AE2" s="7"/>
-      <c r="AF2" s="7"/>
-      <c r="AG2" s="8"/>
-      <c r="AH2" s="7"/>
-      <c r="AI2" s="7"/>
-      <c r="AJ2" s="6"/>
-      <c r="AK2" s="6"/>
-      <c r="AM2" s="6"/>
-    </row>
-    <row r="3" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="10" t="s">
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="4"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AM2" s="2"/>
+    </row>
+    <row r="3" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="N3" s="12" t="s">
+      <c r="N3" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="P3" s="13" t="s">
+      <c r="P3" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="Q3" s="12" t="s">
+      <c r="Q3" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="U3" s="14" t="s">
+      <c r="U3" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V3" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W3" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X3" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="Y3" s="7"/>
-      <c r="Z3" s="7"/>
-      <c r="AA3" s="7"/>
-      <c r="AB3" s="5"/>
-      <c r="AC3" s="7"/>
-      <c r="AD3" s="7"/>
-      <c r="AE3" s="7"/>
-      <c r="AF3" s="7"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="7"/>
-      <c r="AI3" s="7"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AM3" s="6"/>
-    </row>
-    <row r="4" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="2"/>
+      <c r="AK3" s="2"/>
+      <c r="AM3" s="2"/>
+    </row>
+    <row r="4" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="L4" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="8" t="s">
         <v>307</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="O4" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="P4" s="13" t="s">
+      <c r="P4" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="Q4" s="12" t="s">
+      <c r="Q4" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="R4" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="S4" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="T4" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="U4" s="14" t="s">
+      <c r="U4" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="V4" s="7"/>
-      <c r="W4" s="7"/>
-      <c r="Y4" s="7"/>
-      <c r="Z4" s="7"/>
-      <c r="AA4" s="7"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="7"/>
-      <c r="AD4" s="7"/>
-      <c r="AE4" s="7"/>
-      <c r="AF4" s="7"/>
-      <c r="AG4" s="8"/>
-      <c r="AI4" s="7"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="6"/>
-      <c r="AM4" s="6"/>
-    </row>
-    <row r="5" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="3"/>
+      <c r="AD4" s="3"/>
+      <c r="AE4" s="3"/>
+      <c r="AF4" s="3"/>
+      <c r="AG4" s="4"/>
+      <c r="AI4" s="3"/>
+      <c r="AJ4" s="2"/>
+      <c r="AK4" s="2"/>
+      <c r="AM4" s="2"/>
+    </row>
+    <row r="5" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="9" t="s">
         <v>227</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P5" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="Q5" s="12" t="s">
+      <c r="Q5" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="R5" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="S5" s="7"/>
-      <c r="V5" s="7"/>
-      <c r="W5" s="7"/>
-      <c r="Y5" s="7"/>
-      <c r="Z5" s="7"/>
-      <c r="AA5" s="7"/>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="7"/>
-      <c r="AD5" s="7"/>
-      <c r="AE5" s="7"/>
-      <c r="AG5" s="8"/>
-      <c r="AJ5" s="6"/>
-      <c r="AK5" s="6"/>
-      <c r="AM5" s="6"/>
-    </row>
-    <row r="6" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AG5" s="4"/>
+      <c r="AJ5" s="2"/>
+      <c r="AK5" s="2"/>
+      <c r="AM5" s="2"/>
+    </row>
+    <row r="6" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P6" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="Q6" s="12" t="s">
+      <c r="Q6" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="S6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="Y6" s="7"/>
-      <c r="Z6" s="7"/>
-      <c r="AA6" s="7"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="7"/>
-      <c r="AD6" s="7"/>
-      <c r="AE6" s="7"/>
-      <c r="AG6" s="8"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AM6" s="6"/>
-    </row>
-    <row r="7" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AG6" s="4"/>
+      <c r="AJ6" s="2"/>
+      <c r="AK6" s="2"/>
+      <c r="AM6" s="2"/>
+    </row>
+    <row r="7" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="N7" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="S7" s="7"/>
-      <c r="V7" s="7"/>
-      <c r="W7" s="7"/>
-      <c r="Y7" s="7"/>
-      <c r="Z7" s="7"/>
-      <c r="AA7" s="7"/>
-      <c r="AB7" s="5"/>
-      <c r="AC7" s="7"/>
-      <c r="AD7" s="7"/>
-      <c r="AJ7" s="6"/>
-    </row>
-    <row r="8" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AJ7" s="2"/>
+    </row>
+    <row r="8" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="M8" s="7"/>
-      <c r="S8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
-      <c r="AA8" s="7"/>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="7"/>
-      <c r="AD8" s="7"/>
-      <c r="AJ8" s="6"/>
-    </row>
-    <row r="9" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AJ8" s="2"/>
+    </row>
+    <row r="9" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>278</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="I9" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="V9" s="7"/>
-      <c r="W9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AA9" s="7"/>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="7"/>
-      <c r="AD9" s="7"/>
-      <c r="AJ9" s="6"/>
-    </row>
-    <row r="10" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AJ9" s="2"/>
+    </row>
+    <row r="10" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="S10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AA10" s="7"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="7"/>
-      <c r="AD10" s="7"/>
-      <c r="AJ10" s="6"/>
-    </row>
-    <row r="11" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="1"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AJ10" s="2"/>
+    </row>
+    <row r="11" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>279</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="I11" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="V11" s="7"/>
-      <c r="W11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AA11" s="7"/>
-      <c r="AB11" s="5"/>
-      <c r="AC11" s="7"/>
-      <c r="AD11" s="7"/>
-      <c r="AJ11" s="6"/>
-    </row>
-    <row r="12" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="1"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AJ11" s="2"/>
+    </row>
+    <row r="12" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="8" t="s">
         <v>277</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="I12" s="2" t="s">
+      <c r="I12" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="S12" s="7"/>
-      <c r="V12" s="7"/>
-      <c r="W12" s="7"/>
-      <c r="Y12" s="7"/>
-      <c r="Z12" s="7"/>
-      <c r="AA12" s="7"/>
-      <c r="AB12" s="5"/>
-      <c r="AC12" s="7"/>
-      <c r="AD12" s="7"/>
-      <c r="AJ12" s="6"/>
-    </row>
-    <row r="13" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="8"/>
+      <c r="R12" s="8"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="8"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="1"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AJ12" s="2"/>
+    </row>
+    <row r="13" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="9" t="s">
         <v>314</v>
       </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="S13" s="7"/>
-      <c r="V13" s="7"/>
-      <c r="W13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7"/>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="5"/>
-      <c r="AC13" s="7"/>
-      <c r="AD13" s="7"/>
-      <c r="AJ13" s="6"/>
-    </row>
-    <row r="14" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
+      <c r="H13" s="9"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="1"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AJ13" s="2"/>
+    </row>
+    <row r="14" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="S14" s="7"/>
-      <c r="V14" s="7"/>
-      <c r="W14" s="7"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="5"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
-      <c r="AJ14" s="6"/>
-    </row>
-    <row r="15" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="8"/>
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="8"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AJ14" s="2"/>
+    </row>
+    <row r="15" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="S15" s="7"/>
-      <c r="V15" s="7"/>
-      <c r="W15" s="7"/>
-      <c r="Y15" s="7"/>
-      <c r="Z15" s="7"/>
-      <c r="AA15" s="7"/>
-      <c r="AB15" s="5"/>
-      <c r="AC15" s="7"/>
-      <c r="AD15" s="7"/>
-      <c r="AJ15" s="6"/>
-    </row>
-    <row r="16" spans="1:39" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="1"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AJ15" s="2"/>
+    </row>
+    <row r="16" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="V16" s="7"/>
-      <c r="W16" s="7"/>
-      <c r="Y16" s="7"/>
-      <c r="Z16" s="7"/>
-      <c r="AA16" s="7"/>
-      <c r="AB16" s="5"/>
-      <c r="AC16" s="7"/>
-      <c r="AD16" s="7"/>
-      <c r="AJ16" s="6"/>
-    </row>
-    <row r="17" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="8"/>
+      <c r="R16" s="8"/>
+      <c r="S16" s="8"/>
+      <c r="T16" s="8"/>
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="8"/>
+      <c r="X16" s="8"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AJ16" s="2"/>
+    </row>
+    <row r="17" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="S17" s="7"/>
-      <c r="V17" s="7"/>
-      <c r="W17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-      <c r="AA17" s="7"/>
-      <c r="AB17" s="5"/>
-      <c r="AC17" s="7"/>
-      <c r="AD17" s="7"/>
-      <c r="AJ17" s="6"/>
-    </row>
-    <row r="18" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="3"/>
+      <c r="AD17" s="3"/>
+      <c r="AJ17" s="2"/>
+    </row>
+    <row r="18" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="S18" s="7"/>
-      <c r="V18" s="7"/>
-      <c r="W18" s="7"/>
-      <c r="Y18" s="7"/>
-      <c r="Z18" s="7"/>
-      <c r="AA18" s="7"/>
-      <c r="AB18" s="5"/>
-      <c r="AC18" s="7"/>
-      <c r="AJ18" s="6"/>
-    </row>
-    <row r="19" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="8"/>
+      <c r="R18" s="8"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="8"/>
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="8"/>
+      <c r="X18" s="8"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="3"/>
+      <c r="AJ18" s="2"/>
+    </row>
+    <row r="19" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="S19" s="7"/>
-      <c r="V19" s="7"/>
-      <c r="W19" s="7"/>
-      <c r="Y19" s="7"/>
-      <c r="Z19" s="7"/>
-      <c r="AA19" s="7"/>
-      <c r="AB19" s="5"/>
-      <c r="AC19" s="7"/>
-      <c r="AJ19" s="6"/>
-    </row>
-    <row r="20" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="3"/>
+      <c r="AJ19" s="2"/>
+    </row>
+    <row r="20" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="B20" s="12" t="s">
+      <c r="B20" s="8" t="s">
         <v>283</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="S20" s="7"/>
-      <c r="V20" s="7"/>
-      <c r="W20" s="7"/>
-      <c r="Y20" s="7"/>
-      <c r="Z20" s="7"/>
-      <c r="AA20" s="7"/>
-      <c r="AB20" s="5"/>
-      <c r="AC20" s="7"/>
-      <c r="AJ20" s="6"/>
-    </row>
-    <row r="21" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="8"/>
+      <c r="R20" s="8"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="8"/>
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="8"/>
+      <c r="X20" s="8"/>
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="3"/>
+      <c r="AJ20" s="2"/>
+    </row>
+    <row r="21" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="5"/>
-      <c r="AC21" s="7"/>
-      <c r="AJ21" s="6"/>
-    </row>
-    <row r="22" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="3"/>
+      <c r="AJ21" s="2"/>
+    </row>
+    <row r="22" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="S22" s="7"/>
-      <c r="V22" s="7"/>
-      <c r="W22" s="7"/>
-      <c r="Y22" s="7"/>
-      <c r="Z22" s="7"/>
-      <c r="AA22" s="7"/>
-      <c r="AB22" s="5"/>
-      <c r="AC22" s="7"/>
-      <c r="AJ22" s="6"/>
-    </row>
-    <row r="23" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="8"/>
+      <c r="R22" s="8"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="8"/>
+      <c r="U22" s="8"/>
+      <c r="V22" s="8"/>
+      <c r="W22" s="8"/>
+      <c r="X22" s="8"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="3"/>
+      <c r="AJ22" s="2"/>
+    </row>
+    <row r="23" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="S23" s="7"/>
-      <c r="V23" s="7"/>
-      <c r="W23" s="7"/>
-      <c r="Y23" s="7"/>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="7"/>
-      <c r="AJ23" s="6"/>
-    </row>
-    <row r="24" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="3"/>
+      <c r="AJ23" s="2"/>
+    </row>
+    <row r="24" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="S24" s="7"/>
-      <c r="V24" s="7"/>
-      <c r="W24" s="7"/>
-      <c r="Y24" s="7"/>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="7"/>
-      <c r="AB24" s="5"/>
-      <c r="AC24" s="7"/>
-      <c r="AJ24" s="6"/>
-    </row>
-    <row r="25" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="8"/>
+      <c r="X24" s="8"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="3"/>
+      <c r="AJ24" s="2"/>
+    </row>
+    <row r="25" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="9" t="s">
         <v>287</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="S25" s="7"/>
-      <c r="V25" s="7"/>
-      <c r="W25" s="7"/>
-      <c r="Y25" s="7"/>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="7"/>
-      <c r="AB25" s="5"/>
-      <c r="AC25" s="7"/>
-      <c r="AJ25" s="6"/>
-    </row>
-    <row r="26" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="3"/>
+      <c r="AJ25" s="2"/>
+    </row>
+    <row r="26" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="S26" s="7"/>
-      <c r="V26" s="7"/>
-      <c r="W26" s="7"/>
-      <c r="Y26" s="7"/>
-      <c r="Z26" s="7"/>
-      <c r="AA26" s="7"/>
-      <c r="AB26" s="5"/>
-      <c r="AC26" s="7"/>
-      <c r="AJ26" s="6"/>
-    </row>
-    <row r="27" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="10" t="s">
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="3"/>
+      <c r="AJ26" s="2"/>
+    </row>
+    <row r="27" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="S27" s="7"/>
-      <c r="V27" s="7"/>
-      <c r="W27" s="7"/>
-      <c r="Y27" s="7"/>
-      <c r="Z27" s="7"/>
-      <c r="AA27" s="7"/>
-      <c r="AB27" s="5"/>
-      <c r="AC27" s="7"/>
-      <c r="AJ27" s="6"/>
-    </row>
-    <row r="28" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="10" t="s">
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="3"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="3"/>
+      <c r="AJ27" s="2"/>
+    </row>
+    <row r="28" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="S28" s="7"/>
-      <c r="V28" s="7"/>
-      <c r="W28" s="7"/>
-      <c r="Y28" s="7"/>
-      <c r="Z28" s="7"/>
-      <c r="AA28" s="7"/>
-      <c r="AB28" s="5"/>
-      <c r="AC28" s="7"/>
-      <c r="AJ28" s="6"/>
-    </row>
-    <row r="29" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="8"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="8"/>
+      <c r="Q28" s="8"/>
+      <c r="R28" s="8"/>
+      <c r="S28" s="8"/>
+      <c r="T28" s="8"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="3"/>
+      <c r="AJ28" s="2"/>
+    </row>
+    <row r="29" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="S29" s="7"/>
-      <c r="V29" s="7"/>
-      <c r="W29" s="7"/>
-      <c r="Y29" s="7"/>
-      <c r="Z29" s="7"/>
-      <c r="AA29" s="7"/>
-      <c r="AB29" s="5"/>
-      <c r="AC29" s="7"/>
-      <c r="AJ29" s="6"/>
-    </row>
-    <row r="30" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="10" t="s">
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9"/>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="3"/>
+      <c r="AJ29" s="2"/>
+    </row>
+    <row r="30" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B30" s="12" t="s">
+      <c r="B30" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-      <c r="S30" s="7"/>
-      <c r="V30" s="7"/>
-      <c r="W30" s="7"/>
-      <c r="Y30" s="7"/>
-      <c r="Z30" s="7"/>
-      <c r="AA30" s="7"/>
-      <c r="AB30" s="5"/>
-      <c r="AC30" s="7"/>
-      <c r="AJ30" s="6"/>
-    </row>
-    <row r="31" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="8"/>
+      <c r="Q30" s="8"/>
+      <c r="R30" s="8"/>
+      <c r="S30" s="8"/>
+      <c r="T30" s="8"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8"/>
+      <c r="X30" s="8"/>
+      <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="3"/>
+      <c r="AJ30" s="2"/>
+    </row>
+    <row r="31" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="9" t="s">
         <v>312</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-      <c r="S31" s="7"/>
-      <c r="V31" s="7"/>
-      <c r="W31" s="7"/>
-      <c r="Y31" s="7"/>
-      <c r="Z31" s="7"/>
-      <c r="AA31" s="7"/>
-      <c r="AB31" s="5"/>
-      <c r="AC31" s="7"/>
-      <c r="AJ31" s="6"/>
-    </row>
-    <row r="32" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="10" t="s">
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+      <c r="M31" s="9"/>
+      <c r="N31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="3"/>
+      <c r="AJ31" s="2"/>
+    </row>
+    <row r="32" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B32" s="12" t="s">
+      <c r="B32" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="8" t="s">
         <v>313</v>
       </c>
-      <c r="E32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="S32" s="7"/>
-      <c r="V32" s="7"/>
-      <c r="W32" s="7"/>
-      <c r="Y32" s="7"/>
-      <c r="Z32" s="7"/>
-      <c r="AA32" s="7"/>
-      <c r="AB32" s="5"/>
-      <c r="AC32" s="7"/>
-      <c r="AJ32" s="6"/>
-    </row>
-    <row r="33" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="10" t="s">
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="8"/>
+      <c r="Q32" s="8"/>
+      <c r="R32" s="8"/>
+      <c r="S32" s="8"/>
+      <c r="T32" s="8"/>
+      <c r="U32" s="8"/>
+      <c r="V32" s="8"/>
+      <c r="W32" s="8"/>
+      <c r="X32" s="8"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="3"/>
+      <c r="AJ32" s="2"/>
+    </row>
+    <row r="33" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="7"/>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-      <c r="S33" s="7"/>
-      <c r="V33" s="7"/>
-      <c r="W33" s="7"/>
-      <c r="Y33" s="7"/>
-      <c r="Z33" s="7"/>
-      <c r="AA33" s="7"/>
-      <c r="AB33" s="5"/>
-      <c r="AC33" s="7"/>
-      <c r="AJ33" s="6"/>
-    </row>
-    <row r="34" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="10" t="s">
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="3"/>
+      <c r="AJ33" s="2"/>
+    </row>
+    <row r="34" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-      <c r="S34" s="7"/>
-      <c r="V34" s="7"/>
-      <c r="W34" s="7"/>
-      <c r="Y34" s="7"/>
-      <c r="Z34" s="7"/>
-      <c r="AA34" s="7"/>
-      <c r="AB34" s="5"/>
-      <c r="AC34" s="7"/>
-      <c r="AJ34" s="6"/>
-    </row>
-    <row r="35" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="10" t="s">
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="8"/>
+      <c r="N34" s="8"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="8"/>
+      <c r="Q34" s="8"/>
+      <c r="R34" s="8"/>
+      <c r="S34" s="8"/>
+      <c r="T34" s="8"/>
+      <c r="U34" s="8"/>
+      <c r="V34" s="8"/>
+      <c r="W34" s="8"/>
+      <c r="X34" s="8"/>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="3"/>
+      <c r="AJ34" s="2"/>
+    </row>
+    <row r="35" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B35" s="12" t="s">
+      <c r="B35" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-      <c r="S35" s="7"/>
-      <c r="V35" s="7"/>
-      <c r="W35" s="7"/>
-      <c r="Y35" s="7"/>
-      <c r="Z35" s="7"/>
-      <c r="AA35" s="7"/>
-      <c r="AB35" s="5"/>
-      <c r="AC35" s="7"/>
-      <c r="AJ35" s="6"/>
-    </row>
-    <row r="36" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="10" t="s">
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+      <c r="M35" s="9"/>
+      <c r="N35" s="9"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="3"/>
+      <c r="AJ35" s="2"/>
+    </row>
+    <row r="36" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B36" s="12" t="s">
+      <c r="B36" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="S36" s="7"/>
-      <c r="V36" s="7"/>
-      <c r="W36" s="7"/>
-      <c r="Y36" s="7"/>
-      <c r="Z36" s="7"/>
-      <c r="AA36" s="7"/>
-      <c r="AB36" s="5"/>
-      <c r="AC36" s="7"/>
-      <c r="AJ36" s="6"/>
-    </row>
-    <row r="37" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="10" t="s">
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+      <c r="M36" s="8"/>
+      <c r="N36" s="8"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
+      <c r="Q36" s="8"/>
+      <c r="R36" s="8"/>
+      <c r="S36" s="8"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="8"/>
+      <c r="V36" s="8"/>
+      <c r="W36" s="8"/>
+      <c r="X36" s="8"/>
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="3"/>
+      <c r="AJ36" s="2"/>
+    </row>
+    <row r="37" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-      <c r="S37" s="7"/>
-      <c r="V37" s="7"/>
-      <c r="W37" s="7"/>
-      <c r="Y37" s="7"/>
-      <c r="Z37" s="7"/>
-      <c r="AA37" s="7"/>
-      <c r="AB37" s="5"/>
-      <c r="AC37" s="7"/>
-      <c r="AJ37" s="6"/>
-    </row>
-    <row r="38" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="10" t="s">
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="3"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="3"/>
+      <c r="AJ37" s="2"/>
+    </row>
+    <row r="38" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="8" t="s">
         <v>318</v>
       </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-      <c r="S38" s="7"/>
-      <c r="V38" s="7"/>
-      <c r="W38" s="7"/>
-      <c r="Y38" s="7"/>
-      <c r="Z38" s="7"/>
-      <c r="AA38" s="7"/>
-      <c r="AB38" s="5"/>
-      <c r="AC38" s="7"/>
-      <c r="AJ38" s="6"/>
-    </row>
-    <row r="39" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="10" t="s">
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+      <c r="M38" s="8"/>
+      <c r="N38" s="8"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="8"/>
+      <c r="Q38" s="8"/>
+      <c r="R38" s="8"/>
+      <c r="S38" s="8"/>
+      <c r="T38" s="8"/>
+      <c r="U38" s="8"/>
+      <c r="V38" s="8"/>
+      <c r="W38" s="8"/>
+      <c r="X38" s="8"/>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="3"/>
+      <c r="AJ38" s="2"/>
+    </row>
+    <row r="39" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-      <c r="S39" s="7"/>
-      <c r="V39" s="7"/>
-      <c r="W39" s="7"/>
-      <c r="Y39" s="7"/>
-      <c r="Z39" s="7"/>
-      <c r="AA39" s="7"/>
-      <c r="AB39" s="5"/>
-      <c r="AC39" s="7"/>
-      <c r="AJ39" s="6"/>
-    </row>
-    <row r="40" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="10" t="s">
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+      <c r="M39" s="9"/>
+      <c r="N39" s="9"/>
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="3"/>
+      <c r="AJ39" s="2"/>
+    </row>
+    <row r="40" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="8" t="s">
         <v>269</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="7"/>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-      <c r="S40" s="7"/>
-      <c r="V40" s="7"/>
-      <c r="W40" s="7"/>
-      <c r="Y40" s="7"/>
-      <c r="Z40" s="7"/>
-      <c r="AA40" s="7"/>
-      <c r="AB40" s="5"/>
-      <c r="AC40" s="7"/>
-      <c r="AJ40" s="6"/>
-    </row>
-    <row r="41" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="10" t="s">
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="M40" s="8"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="8"/>
+      <c r="Q40" s="8"/>
+      <c r="R40" s="8"/>
+      <c r="S40" s="8"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="8"/>
+      <c r="V40" s="8"/>
+      <c r="W40" s="8"/>
+      <c r="X40" s="8"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="3"/>
+      <c r="AJ40" s="2"/>
+    </row>
+    <row r="41" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-      <c r="S41" s="7"/>
-      <c r="V41" s="7"/>
-      <c r="W41" s="7"/>
-      <c r="Y41" s="7"/>
-      <c r="Z41" s="7"/>
-      <c r="AA41" s="7"/>
-      <c r="AB41" s="5"/>
-      <c r="AC41" s="7"/>
-      <c r="AJ41" s="6"/>
-    </row>
-    <row r="42" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="10" t="s">
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+      <c r="M41" s="9"/>
+      <c r="N41" s="9"/>
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="3"/>
+      <c r="AJ41" s="2"/>
+    </row>
+    <row r="42" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-      <c r="S42" s="7"/>
-      <c r="V42" s="7"/>
-      <c r="W42" s="7"/>
-      <c r="Y42" s="7"/>
-      <c r="Z42" s="7"/>
-      <c r="AA42" s="7"/>
-      <c r="AB42" s="5"/>
-      <c r="AC42" s="7"/>
-      <c r="AJ42" s="6"/>
-    </row>
-    <row r="43" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="10" t="s">
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="M42" s="8"/>
+      <c r="N42" s="8"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="8"/>
+      <c r="Q42" s="8"/>
+      <c r="R42" s="8"/>
+      <c r="S42" s="8"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="8"/>
+      <c r="V42" s="8"/>
+      <c r="W42" s="8"/>
+      <c r="X42" s="8"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="3"/>
+      <c r="AJ42" s="2"/>
+    </row>
+    <row r="43" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B43" s="12" t="s">
+      <c r="B43" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="7"/>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-      <c r="S43" s="7"/>
-      <c r="V43" s="7"/>
-      <c r="W43" s="7"/>
-      <c r="Y43" s="7"/>
-      <c r="Z43" s="7"/>
-      <c r="AA43" s="7"/>
-      <c r="AB43" s="5"/>
-      <c r="AC43" s="7"/>
-      <c r="AJ43" s="6"/>
-    </row>
-    <row r="44" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="10" t="s">
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+      <c r="M43" s="9"/>
+      <c r="N43" s="9"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="3"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="3"/>
+      <c r="AJ43" s="2"/>
+    </row>
+    <row r="44" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B44" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-      <c r="S44" s="7"/>
-      <c r="V44" s="7"/>
-      <c r="W44" s="7"/>
-      <c r="Y44" s="7"/>
-      <c r="Z44" s="7"/>
-      <c r="AA44" s="7"/>
-      <c r="AB44" s="5"/>
-      <c r="AC44" s="7"/>
-      <c r="AJ44" s="6"/>
-    </row>
-    <row r="45" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="10" t="s">
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="M44" s="8"/>
+      <c r="N44" s="8"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="8"/>
+      <c r="Q44" s="8"/>
+      <c r="R44" s="8"/>
+      <c r="S44" s="8"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="8"/>
+      <c r="V44" s="8"/>
+      <c r="W44" s="8"/>
+      <c r="X44" s="8"/>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="3"/>
+      <c r="AJ44" s="2"/>
+    </row>
+    <row r="45" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="S45" s="7"/>
-      <c r="V45" s="7"/>
-      <c r="W45" s="7"/>
-      <c r="Y45" s="7"/>
-      <c r="Z45" s="7"/>
-      <c r="AA45" s="7"/>
-      <c r="AB45" s="5"/>
-      <c r="AC45" s="7"/>
-      <c r="AJ45" s="6"/>
-    </row>
-    <row r="46" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="10" t="s">
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+      <c r="M45" s="9"/>
+      <c r="N45" s="9"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="3"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="3"/>
+      <c r="AJ45" s="2"/>
+    </row>
+    <row r="46" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="8" t="s">
         <v>274</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="S46" s="7"/>
-      <c r="V46" s="7"/>
-      <c r="W46" s="7"/>
-      <c r="Y46" s="7"/>
-      <c r="Z46" s="7"/>
-      <c r="AA46" s="7"/>
-      <c r="AB46" s="5"/>
-      <c r="AC46" s="7"/>
-      <c r="AJ46" s="6"/>
-    </row>
-    <row r="47" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="10" t="s">
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+      <c r="M46" s="8"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="8"/>
+      <c r="S46" s="8"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="8"/>
+      <c r="V46" s="8"/>
+      <c r="W46" s="8"/>
+      <c r="X46" s="8"/>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="3"/>
+      <c r="AJ46" s="2"/>
+    </row>
+    <row r="47" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="S47" s="7"/>
-      <c r="V47" s="7"/>
-      <c r="W47" s="7"/>
-      <c r="Y47" s="7"/>
-      <c r="Z47" s="7"/>
-      <c r="AA47" s="7"/>
-      <c r="AB47" s="5"/>
-      <c r="AC47" s="7"/>
-      <c r="AJ47" s="6"/>
-    </row>
-    <row r="48" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="10" t="s">
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
+      <c r="X47" s="9"/>
+      <c r="Y47" s="3"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="3"/>
+      <c r="AJ47" s="2"/>
+    </row>
+    <row r="48" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="S48" s="7"/>
-      <c r="V48" s="7"/>
-      <c r="W48" s="7"/>
-      <c r="Y48" s="7"/>
-      <c r="Z48" s="7"/>
-      <c r="AA48" s="7"/>
-      <c r="AB48" s="5"/>
-      <c r="AC48" s="7"/>
-      <c r="AJ48" s="6"/>
-    </row>
-    <row r="49" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="10" t="s">
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+      <c r="M48" s="8"/>
+      <c r="N48" s="8"/>
+      <c r="O48" s="8"/>
+      <c r="P48" s="8"/>
+      <c r="Q48" s="8"/>
+      <c r="R48" s="8"/>
+      <c r="S48" s="8"/>
+      <c r="T48" s="8"/>
+      <c r="U48" s="8"/>
+      <c r="V48" s="8"/>
+      <c r="W48" s="8"/>
+      <c r="X48" s="8"/>
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="3"/>
+      <c r="AJ48" s="2"/>
+    </row>
+    <row r="49" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="S49" s="7"/>
-      <c r="V49" s="7"/>
-      <c r="W49" s="7"/>
-      <c r="Y49" s="7"/>
-      <c r="Z49" s="7"/>
-      <c r="AA49" s="7"/>
-      <c r="AB49" s="5"/>
-      <c r="AC49" s="7"/>
-      <c r="AJ49" s="6"/>
-    </row>
-    <row r="50" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="10" t="s">
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="9"/>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="9"/>
+      <c r="R49" s="9"/>
+      <c r="S49" s="9"/>
+      <c r="T49" s="9"/>
+      <c r="U49" s="9"/>
+      <c r="V49" s="9"/>
+      <c r="W49" s="9"/>
+      <c r="X49" s="9"/>
+      <c r="Y49" s="3"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
+      <c r="AB49" s="1"/>
+      <c r="AC49" s="3"/>
+      <c r="AJ49" s="2"/>
+    </row>
+    <row r="50" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="S50" s="7"/>
-      <c r="V50" s="7"/>
-      <c r="W50" s="7"/>
-      <c r="Y50" s="7"/>
-      <c r="Z50" s="7"/>
-      <c r="AA50" s="7"/>
-      <c r="AB50" s="5"/>
-      <c r="AC50" s="7"/>
-      <c r="AJ50" s="6"/>
-    </row>
-    <row r="51" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="10" t="s">
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
+      <c r="Q50" s="8"/>
+      <c r="R50" s="8"/>
+      <c r="S50" s="8"/>
+      <c r="T50" s="8"/>
+      <c r="U50" s="8"/>
+      <c r="V50" s="8"/>
+      <c r="W50" s="8"/>
+      <c r="X50" s="8"/>
+      <c r="Y50" s="3"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="3"/>
+      <c r="AJ50" s="2"/>
+    </row>
+    <row r="51" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-      <c r="S51" s="7"/>
-      <c r="V51" s="7"/>
-      <c r="W51" s="7"/>
-      <c r="Y51" s="7"/>
-      <c r="Z51" s="7"/>
-      <c r="AA51" s="7"/>
-      <c r="AB51" s="5"/>
-      <c r="AC51" s="7"/>
-      <c r="AJ51" s="6"/>
-    </row>
-    <row r="52" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="10" t="s">
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="9"/>
+      <c r="O51" s="9"/>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="9"/>
+      <c r="V51" s="9"/>
+      <c r="W51" s="9"/>
+      <c r="X51" s="9"/>
+      <c r="Y51" s="3"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="3"/>
+      <c r="AJ51" s="2"/>
+    </row>
+    <row r="52" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="C52" s="7"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="S52" s="7"/>
-      <c r="V52" s="7"/>
-      <c r="W52" s="7"/>
-      <c r="Y52" s="7"/>
-      <c r="Z52" s="7"/>
-      <c r="AA52" s="7"/>
-      <c r="AB52" s="5"/>
-      <c r="AC52" s="7"/>
-    </row>
-    <row r="53" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="10" t="s">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="Q52" s="8"/>
+      <c r="R52" s="8"/>
+      <c r="S52" s="8"/>
+      <c r="T52" s="8"/>
+      <c r="U52" s="8"/>
+      <c r="V52" s="8"/>
+      <c r="W52" s="8"/>
+      <c r="X52" s="8"/>
+      <c r="Y52" s="3"/>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
+      <c r="AB52" s="1"/>
+      <c r="AC52" s="3"/>
+    </row>
+    <row r="53" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="S53" s="7"/>
-      <c r="V53" s="7"/>
-      <c r="W53" s="7"/>
-      <c r="Y53" s="7"/>
-      <c r="Z53" s="7"/>
-      <c r="AA53" s="7"/>
-      <c r="AB53" s="5"/>
-      <c r="AC53" s="7"/>
-    </row>
-    <row r="54" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="10" t="s">
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+      <c r="M53" s="9"/>
+      <c r="N53" s="9"/>
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="9"/>
+      <c r="R53" s="9"/>
+      <c r="S53" s="9"/>
+      <c r="T53" s="9"/>
+      <c r="U53" s="9"/>
+      <c r="V53" s="9"/>
+      <c r="W53" s="9"/>
+      <c r="X53" s="9"/>
+      <c r="Y53" s="3"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
+      <c r="AB53" s="1"/>
+      <c r="AC53" s="3"/>
+    </row>
+    <row r="54" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
-      <c r="G54" s="7"/>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
-      <c r="S54" s="7"/>
-      <c r="V54" s="7"/>
-      <c r="W54" s="7"/>
-      <c r="Y54" s="7"/>
-      <c r="Z54" s="7"/>
-      <c r="AA54" s="7"/>
-      <c r="AB54" s="5"/>
-      <c r="AC54" s="7"/>
-    </row>
-    <row r="55" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="10" t="s">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
+      <c r="Q54" s="8"/>
+      <c r="R54" s="8"/>
+      <c r="S54" s="8"/>
+      <c r="T54" s="8"/>
+      <c r="U54" s="8"/>
+      <c r="V54" s="8"/>
+      <c r="W54" s="8"/>
+      <c r="X54" s="8"/>
+      <c r="Y54" s="3"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
+      <c r="AB54" s="1"/>
+      <c r="AC54" s="3"/>
+    </row>
+    <row r="55" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
-      <c r="S55" s="7"/>
-      <c r="V55" s="7"/>
-      <c r="W55" s="7"/>
-      <c r="Y55" s="7"/>
-      <c r="Z55" s="7"/>
-      <c r="AA55" s="7"/>
-      <c r="AB55" s="5"/>
-      <c r="AC55" s="7"/>
-    </row>
-    <row r="56" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="10" t="s">
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+      <c r="N55" s="9"/>
+      <c r="O55" s="9"/>
+      <c r="P55" s="9"/>
+      <c r="Q55" s="9"/>
+      <c r="R55" s="9"/>
+      <c r="S55" s="9"/>
+      <c r="T55" s="9"/>
+      <c r="U55" s="9"/>
+      <c r="V55" s="9"/>
+      <c r="W55" s="9"/>
+      <c r="X55" s="9"/>
+      <c r="Y55" s="3"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="1"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
-      <c r="G56" s="7"/>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="J56" s="7"/>
-      <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
-      <c r="M56" s="7"/>
-      <c r="S56" s="7"/>
-      <c r="V56" s="7"/>
-      <c r="W56" s="7"/>
-      <c r="Y56" s="7"/>
-      <c r="Z56" s="7"/>
-      <c r="AA56" s="7"/>
-      <c r="AB56" s="5"/>
-      <c r="AC56" s="7"/>
-    </row>
-    <row r="57" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="8"/>
+      <c r="S56" s="8"/>
+      <c r="T56" s="8"/>
+      <c r="U56" s="8"/>
+      <c r="V56" s="8"/>
+      <c r="W56" s="8"/>
+      <c r="X56" s="8"/>
+      <c r="Y56" s="3"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="1"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="J57" s="7"/>
-      <c r="K57" s="7"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
-      <c r="S57" s="7"/>
-      <c r="V57" s="7"/>
-      <c r="W57" s="7"/>
-      <c r="Y57" s="7"/>
-      <c r="Z57" s="7"/>
-      <c r="AA57" s="7"/>
-      <c r="AB57" s="5"/>
-      <c r="AC57" s="7"/>
-    </row>
-    <row r="58" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="10" t="s">
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+      <c r="M57" s="9"/>
+      <c r="N57" s="9"/>
+      <c r="O57" s="9"/>
+      <c r="P57" s="9"/>
+      <c r="Q57" s="9"/>
+      <c r="R57" s="9"/>
+      <c r="S57" s="9"/>
+      <c r="T57" s="9"/>
+      <c r="U57" s="9"/>
+      <c r="V57" s="9"/>
+      <c r="W57" s="9"/>
+      <c r="X57" s="9"/>
+      <c r="Y57" s="3"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
+      <c r="AB57" s="1"/>
+      <c r="AC57" s="3"/>
+    </row>
+    <row r="58" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="G58" s="7"/>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
-      <c r="S58" s="7"/>
-      <c r="V58" s="7"/>
-      <c r="W58" s="7"/>
-      <c r="Y58" s="7"/>
-      <c r="Z58" s="7"/>
-      <c r="AA58" s="7"/>
-      <c r="AB58" s="5"/>
-      <c r="AC58" s="7"/>
-    </row>
-    <row r="59" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="15" t="s">
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8"/>
+      <c r="Q58" s="8"/>
+      <c r="R58" s="8"/>
+      <c r="S58" s="8"/>
+      <c r="T58" s="8"/>
+      <c r="U58" s="8"/>
+      <c r="V58" s="8"/>
+      <c r="W58" s="8"/>
+      <c r="X58" s="8"/>
+      <c r="Y58" s="3"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
+      <c r="AB58" s="1"/>
+      <c r="AC58" s="3"/>
+    </row>
+    <row r="59" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="9" t="s">
         <v>309</v>
       </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+      <c r="M59" s="9"/>
+      <c r="N59" s="9"/>
+      <c r="O59" s="9"/>
+      <c r="P59" s="9"/>
+      <c r="Q59" s="9"/>
+      <c r="R59" s="9"/>
+      <c r="S59" s="9"/>
+      <c r="T59" s="9"/>
+      <c r="U59" s="9"/>
+      <c r="V59" s="9"/>
+      <c r="W59" s="9"/>
+      <c r="X59" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/spreadsheets/franchises.xlsx
+++ b/spreadsheets/franchises.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/willmanicom/StatsAutomator/spreadsheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71870541-4273-8347-BFBB-18746C44DBF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EB4364-DE58-8743-B4BB-A56620E9B280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{560E9FB9-65B9-9A4C-9447-806357BA28D7}"/>
   </bookViews>
